--- a/demo_patient_weight_kg_single_variable_report.xlsx
+++ b/demo_patient_weight_kg_single_variable_report.xlsx
@@ -1169,7 +1169,7 @@
         <v>0.99</v>
       </c>
       <c r="D10" t="n">
-        <v>95.50099999999998</v>
+        <v>95.50100000000002</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1197,7 +1197,7 @@
         <v>0.2</v>
       </c>
       <c r="D12" t="n">
-        <v>58.580000000000005</v>
+        <v>58.58</v>
       </c>
     </row>
     <row r="13" spans="1:4">
